--- a/reports/二级子公司C_利润表_2026-12.xlsx
+++ b/reports/二级子公司C_利润表_2026-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>88070665</v>
+        <v>89979292</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>85522960</v>
+        <v>85442247</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1024808800</v>
+        <v>1023991148</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>399640</v>
+        <v>400713</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4985200</v>
+        <v>4989795</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>349685</v>
+        <v>349772</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4362050</v>
+        <v>4366461</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>299730</v>
+        <v>299061</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3738900</v>
+        <v>3742348</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>279748</v>
+        <v>278539</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3489640</v>
+        <v>3491982</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>149865</v>
+        <v>149019</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1869450</v>
+        <v>1870015</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>119892</v>
+        <v>119175</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1495560</v>
+        <v>1495381</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>86472105</v>
+        <v>88383013</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>83924400</v>
+        <v>83845968</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>79928000</v>
+        <v>79821227</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>955016000</v>
+        <v>954211482</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1198920</v>
+        <v>1200336</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>14955600</v>
+        <v>14940909</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>799280</v>
+        <v>802069</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>9970400</v>
+        <v>9962445</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2997300</v>
+        <v>3012840</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>37389000</v>
+        <v>37371325</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>399640</v>
+        <v>402025</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>4985200</v>
+        <v>4984880</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>299730</v>
+        <v>301438</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3738900</v>
+        <v>3740227</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>499550</v>
+        <v>501762</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>6231500</v>
+        <v>6235934</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>599460</v>
+        <v>600886</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>7477800</v>
+        <v>7484855</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2497750</v>
+        <v>2497526</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>31157500</v>
+        <v>31188950</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>49955</v>
+        <v>51369</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>623150</v>
+        <v>618619</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1193468</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>14964987</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>794682</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>9972867</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>59696225</v>
+        <v>63829706</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>53152120</v>
+        <v>52977254</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>51953200</v>
+        <v>51779539</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>666672032</v>
+        <v>666142815</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1198920</v>
+        <v>1197715</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>14955600</v>
+        <v>14940603</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2001217</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>24901890</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>641827</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>7970246</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>401777</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4983097</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>482442</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>5982193</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>361685</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4488509</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>240790</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2993368</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>200233</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2495002</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>899190</v>
+        <v>898806</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>11216700</v>
+        <v>11227970</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>699370</v>
+        <v>697381</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>8724100</v>
+        <v>8731690</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>599460</v>
+        <v>596606</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>7477800</v>
+        <v>7482153</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4495950</v>
+        <v>4469695</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>56083500</v>
+        <v>56094264</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>199820</v>
+        <v>198643</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2492600</v>
+        <v>2492022</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>349685</v>
+        <v>358731</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4362050</v>
+        <v>4322955</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>399640</v>
+        <v>358731</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4985200</v>
+        <v>4322955</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>49955</v>
+        <v>51465</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>623150</v>
+        <v>617299</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>185740</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2222442</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>351089</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>4358896</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>124279</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1482607</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>93256</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1112478</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>155342</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1854983</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>501521</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>6236409</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>82544</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>989891</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>61753</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>742428</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>102677</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1237154</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>71742</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>865709</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>51196</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>618083</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>40960</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>494232</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30755</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>370522</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26775880</v>
+        <v>25797404</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31321785</v>
+        <v>29078596</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>200250</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2490288</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>51719</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>617533</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>79928</v>
+        <v>82863</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>997040</v>
+        <v>988464</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26695952</v>
+        <v>25914791</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2797480</v>
+        <v>2899296</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>34896400</v>
+        <v>34628250</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>23898472</v>
+        <v>23015495</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>23898472</v>
+        <v>23015495</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>23898472</v>
+        <v>23015495</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>23898472</v>
+        <v>23015495</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>23898472</v>
+        <v>23015495</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
